--- a/Results/detection/Detection_Parameters_Summary.xlsx
+++ b/Results/detection/Detection_Parameters_Summary.xlsx
@@ -13695,22 +13695,22 @@
         </is>
       </c>
       <c r="I230">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J230">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K230">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L230">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M230">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N230">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="231">
@@ -13753,22 +13753,22 @@
         </is>
       </c>
       <c r="I231">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J231">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K231">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L231">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M231">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N231">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="232">
@@ -13811,22 +13811,22 @@
         </is>
       </c>
       <c r="I232">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J232">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K232">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L232">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M232">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N232">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="233">
@@ -13869,22 +13869,22 @@
         </is>
       </c>
       <c r="I233">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J233">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K233">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L233">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M233">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N233">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="234">
@@ -13927,22 +13927,22 @@
         </is>
       </c>
       <c r="I234">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J234">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K234">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L234">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M234">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N234">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="235">
@@ -13985,22 +13985,22 @@
         </is>
       </c>
       <c r="I235">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J235">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K235">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L235">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M235">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N235">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="236">
@@ -14043,22 +14043,22 @@
         </is>
       </c>
       <c r="I236">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J236">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K236">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L236">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M236">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N236">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="237">
@@ -14101,22 +14101,22 @@
         </is>
       </c>
       <c r="I237">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J237">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K237">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L237">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M237">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N237">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="238">
@@ -14159,22 +14159,22 @@
         </is>
       </c>
       <c r="I238">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J238">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K238">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L238">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M238">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N238">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="239">
@@ -14217,22 +14217,22 @@
         </is>
       </c>
       <c r="I239">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J239">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K239">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L239">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M239">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N239">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="240">
@@ -14275,22 +14275,22 @@
         </is>
       </c>
       <c r="I240">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J240">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K240">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L240">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M240">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N240">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="241">
@@ -14333,22 +14333,22 @@
         </is>
       </c>
       <c r="I241">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J241">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K241">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L241">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M241">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N241">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="242">
@@ -14391,22 +14391,22 @@
         </is>
       </c>
       <c r="I242">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J242">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K242">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L242">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M242">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N242">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="243">
@@ -14449,22 +14449,22 @@
         </is>
       </c>
       <c r="I243">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J243">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K243">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L243">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M243">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N243">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="244">
@@ -14507,22 +14507,22 @@
         </is>
       </c>
       <c r="I244">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J244">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K244">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L244">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M244">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N244">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="245">
@@ -14565,22 +14565,22 @@
         </is>
       </c>
       <c r="I245">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J245">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K245">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L245">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M245">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N245">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="246">
@@ -14623,22 +14623,22 @@
         </is>
       </c>
       <c r="I246">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J246">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K246">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L246">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M246">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N246">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="247">
@@ -14681,22 +14681,22 @@
         </is>
       </c>
       <c r="I247">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J247">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K247">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L247">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M247">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N247">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="248">
@@ -14739,22 +14739,22 @@
         </is>
       </c>
       <c r="I248">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J248">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K248">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L248">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M248">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N248">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="249">
@@ -14797,22 +14797,22 @@
         </is>
       </c>
       <c r="I249">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J249">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K249">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L249">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M249">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N249">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="250">
@@ -14855,22 +14855,22 @@
         </is>
       </c>
       <c r="I250">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J250">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K250">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L250">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M250">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N250">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="251">
@@ -14913,22 +14913,22 @@
         </is>
       </c>
       <c r="I251">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J251">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K251">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L251">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M251">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N251">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="252">
@@ -14971,22 +14971,22 @@
         </is>
       </c>
       <c r="I252">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J252">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K252">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L252">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M252">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N252">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="253">
@@ -15029,22 +15029,22 @@
         </is>
       </c>
       <c r="I253">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J253">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K253">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L253">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M253">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N253">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="254">
@@ -15087,22 +15087,22 @@
         </is>
       </c>
       <c r="I254">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J254">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K254">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L254">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M254">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N254">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="255">
@@ -15145,22 +15145,22 @@
         </is>
       </c>
       <c r="I255">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J255">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K255">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L255">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M255">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N255">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="256">
@@ -15203,22 +15203,22 @@
         </is>
       </c>
       <c r="I256">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J256">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K256">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L256">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M256">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N256">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="257">
@@ -15261,22 +15261,22 @@
         </is>
       </c>
       <c r="I257">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J257">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K257">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L257">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M257">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N257">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="258">
@@ -15319,22 +15319,22 @@
         </is>
       </c>
       <c r="I258">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J258">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K258">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L258">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M258">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N258">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="259">
@@ -15377,22 +15377,22 @@
         </is>
       </c>
       <c r="I259">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J259">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K259">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L259">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M259">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N259">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="260">
@@ -15435,22 +15435,22 @@
         </is>
       </c>
       <c r="I260">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J260">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K260">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L260">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M260">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N260">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="261">
@@ -15493,22 +15493,22 @@
         </is>
       </c>
       <c r="I261">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J261">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K261">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L261">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M261">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N261">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="262">
@@ -15551,22 +15551,22 @@
         </is>
       </c>
       <c r="I262">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J262">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K262">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L262">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M262">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N262">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="263">
@@ -15609,22 +15609,22 @@
         </is>
       </c>
       <c r="I263">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J263">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K263">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L263">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M263">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N263">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="264">
@@ -15667,22 +15667,22 @@
         </is>
       </c>
       <c r="I264">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J264">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K264">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L264">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M264">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N264">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="265">
@@ -15725,22 +15725,22 @@
         </is>
       </c>
       <c r="I265">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J265">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K265">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L265">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M265">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N265">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="266">
@@ -15783,22 +15783,22 @@
         </is>
       </c>
       <c r="I266">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J266">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K266">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L266">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M266">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N266">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="267">
@@ -15841,22 +15841,22 @@
         </is>
       </c>
       <c r="I267">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J267">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K267">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L267">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M267">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N267">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="268">
@@ -15899,22 +15899,22 @@
         </is>
       </c>
       <c r="I268">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J268">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K268">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L268">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M268">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N268">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="269">
@@ -15957,22 +15957,22 @@
         </is>
       </c>
       <c r="I269">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J269">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K269">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L269">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M269">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N269">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="270">
@@ -16015,22 +16015,22 @@
         </is>
       </c>
       <c r="I270">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J270">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K270">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L270">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M270">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N270">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="271">
@@ -16073,22 +16073,22 @@
         </is>
       </c>
       <c r="I271">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J271">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K271">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L271">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M271">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N271">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="272">
@@ -16131,22 +16131,22 @@
         </is>
       </c>
       <c r="I272">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J272">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K272">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L272">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M272">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N272">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="273">
@@ -16189,22 +16189,22 @@
         </is>
       </c>
       <c r="I273">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J273">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K273">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L273">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M273">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N273">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="274">
@@ -16247,22 +16247,22 @@
         </is>
       </c>
       <c r="I274">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J274">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K274">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L274">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M274">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N274">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="275">
@@ -16305,22 +16305,22 @@
         </is>
       </c>
       <c r="I275">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J275">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K275">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L275">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M275">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N275">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="276">
@@ -16363,22 +16363,22 @@
         </is>
       </c>
       <c r="I276">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J276">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K276">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L276">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M276">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N276">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="277">
@@ -16421,22 +16421,22 @@
         </is>
       </c>
       <c r="I277">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J277">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K277">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L277">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M277">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N277">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="278">
@@ -16479,22 +16479,22 @@
         </is>
       </c>
       <c r="I278">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J278">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K278">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L278">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M278">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N278">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="279">
@@ -16537,22 +16537,22 @@
         </is>
       </c>
       <c r="I279">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J279">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K279">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L279">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M279">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N279">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="280">
@@ -16595,22 +16595,22 @@
         </is>
       </c>
       <c r="I280">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J280">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K280">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L280">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M280">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N280">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="281">
@@ -16653,22 +16653,22 @@
         </is>
       </c>
       <c r="I281">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J281">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K281">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L281">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M281">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N281">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="282">
@@ -16711,22 +16711,22 @@
         </is>
       </c>
       <c r="I282">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J282">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K282">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L282">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M282">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N282">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="283">
@@ -16769,22 +16769,22 @@
         </is>
       </c>
       <c r="I283">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J283">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K283">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L283">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M283">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N283">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="284">
@@ -16827,22 +16827,22 @@
         </is>
       </c>
       <c r="I284">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J284">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K284">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L284">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M284">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N284">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="285">
@@ -16885,22 +16885,22 @@
         </is>
       </c>
       <c r="I285">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J285">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K285">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L285">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M285">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N285">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="286">
@@ -16943,22 +16943,22 @@
         </is>
       </c>
       <c r="I286">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J286">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K286">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L286">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M286">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N286">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="287">
@@ -17001,22 +17001,22 @@
         </is>
       </c>
       <c r="I287">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J287">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K287">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L287">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M287">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N287">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="288">
@@ -17059,22 +17059,22 @@
         </is>
       </c>
       <c r="I288">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J288">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K288">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L288">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M288">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N288">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="289">
@@ -17117,22 +17117,22 @@
         </is>
       </c>
       <c r="I289">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J289">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K289">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L289">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M289">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N289">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="290">
@@ -17175,22 +17175,22 @@
         </is>
       </c>
       <c r="I290">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J290">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K290">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L290">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M290">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N290">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="291">
@@ -17233,22 +17233,22 @@
         </is>
       </c>
       <c r="I291">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J291">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K291">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L291">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M291">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N291">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="292">
@@ -17291,22 +17291,22 @@
         </is>
       </c>
       <c r="I292">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J292">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K292">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L292">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M292">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N292">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="293">
@@ -17349,22 +17349,22 @@
         </is>
       </c>
       <c r="I293">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J293">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K293">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L293">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M293">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N293">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="294">
@@ -17407,22 +17407,22 @@
         </is>
       </c>
       <c r="I294">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J294">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K294">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L294">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M294">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N294">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="295">
@@ -17465,22 +17465,22 @@
         </is>
       </c>
       <c r="I295">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J295">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K295">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L295">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M295">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N295">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="296">
@@ -17523,22 +17523,22 @@
         </is>
       </c>
       <c r="I296">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J296">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K296">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L296">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M296">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N296">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="297">
@@ -17581,22 +17581,22 @@
         </is>
       </c>
       <c r="I297">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J297">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K297">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L297">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M297">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N297">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="298">
@@ -17639,22 +17639,22 @@
         </is>
       </c>
       <c r="I298">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J298">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K298">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L298">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M298">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N298">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="299">
@@ -17697,22 +17697,22 @@
         </is>
       </c>
       <c r="I299">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J299">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K299">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L299">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M299">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N299">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="300">
@@ -17755,22 +17755,22 @@
         </is>
       </c>
       <c r="I300">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J300">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K300">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L300">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M300">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N300">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="301">
@@ -17813,22 +17813,22 @@
         </is>
       </c>
       <c r="I301">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J301">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K301">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L301">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M301">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N301">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="302">
@@ -17871,22 +17871,22 @@
         </is>
       </c>
       <c r="I302">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J302">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K302">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L302">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M302">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N302">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="303">
@@ -17929,22 +17929,22 @@
         </is>
       </c>
       <c r="I303">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J303">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K303">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L303">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M303">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N303">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="304">
@@ -17987,22 +17987,22 @@
         </is>
       </c>
       <c r="I304">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J304">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K304">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L304">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M304">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N304">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="305">
@@ -18045,22 +18045,22 @@
         </is>
       </c>
       <c r="I305">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J305">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K305">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L305">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M305">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N305">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="306">
@@ -18103,22 +18103,22 @@
         </is>
       </c>
       <c r="I306">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J306">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K306">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L306">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M306">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N306">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="307">
@@ -18161,22 +18161,22 @@
         </is>
       </c>
       <c r="I307">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J307">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K307">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L307">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M307">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N307">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="308">
@@ -18219,22 +18219,22 @@
         </is>
       </c>
       <c r="I308">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J308">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K308">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L308">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M308">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N308">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="309">
@@ -18277,22 +18277,22 @@
         </is>
       </c>
       <c r="I309">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J309">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K309">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L309">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M309">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N309">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="310">
@@ -18335,22 +18335,22 @@
         </is>
       </c>
       <c r="I310">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J310">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K310">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L310">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M310">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N310">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="311">
@@ -18393,22 +18393,22 @@
         </is>
       </c>
       <c r="I311">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J311">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K311">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L311">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M311">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N311">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="312">
@@ -18451,22 +18451,22 @@
         </is>
       </c>
       <c r="I312">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J312">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K312">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L312">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M312">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N312">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="313">
@@ -18509,22 +18509,22 @@
         </is>
       </c>
       <c r="I313">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J313">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K313">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L313">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M313">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N313">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="314">
@@ -18567,22 +18567,22 @@
         </is>
       </c>
       <c r="I314">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J314">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K314">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L314">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M314">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N314">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="315">
@@ -18625,22 +18625,22 @@
         </is>
       </c>
       <c r="I315">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J315">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K315">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L315">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M315">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N315">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="316">
@@ -18683,22 +18683,22 @@
         </is>
       </c>
       <c r="I316">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J316">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K316">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L316">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M316">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N316">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="317">
@@ -18741,22 +18741,22 @@
         </is>
       </c>
       <c r="I317">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J317">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K317">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L317">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M317">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N317">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="318">
@@ -18799,22 +18799,22 @@
         </is>
       </c>
       <c r="I318">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J318">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K318">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L318">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M318">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N318">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="319">
@@ -18857,22 +18857,22 @@
         </is>
       </c>
       <c r="I319">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J319">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K319">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L319">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M319">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N319">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="320">
@@ -18915,22 +18915,22 @@
         </is>
       </c>
       <c r="I320">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J320">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K320">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L320">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M320">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N320">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="321">
@@ -18973,22 +18973,22 @@
         </is>
       </c>
       <c r="I321">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J321">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K321">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L321">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M321">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N321">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="322">
@@ -19031,22 +19031,22 @@
         </is>
       </c>
       <c r="I322">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J322">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K322">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L322">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M322">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N322">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="323">
@@ -19089,22 +19089,22 @@
         </is>
       </c>
       <c r="I323">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J323">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K323">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L323">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M323">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N323">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="324">
@@ -19147,22 +19147,22 @@
         </is>
       </c>
       <c r="I324">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J324">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K324">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L324">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M324">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N324">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="325">
@@ -19205,22 +19205,22 @@
         </is>
       </c>
       <c r="I325">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J325">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K325">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L325">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M325">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N325">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="326">
@@ -19263,22 +19263,22 @@
         </is>
       </c>
       <c r="I326">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J326">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K326">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L326">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M326">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N326">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="327">
@@ -19321,22 +19321,22 @@
         </is>
       </c>
       <c r="I327">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J327">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K327">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L327">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M327">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N327">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="328">
@@ -19379,22 +19379,22 @@
         </is>
       </c>
       <c r="I328">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J328">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K328">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L328">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M328">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N328">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="329">
@@ -19437,22 +19437,22 @@
         </is>
       </c>
       <c r="I329">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J329">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K329">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L329">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M329">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N329">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="330">
@@ -19495,22 +19495,22 @@
         </is>
       </c>
       <c r="I330">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J330">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K330">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L330">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M330">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N330">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="331">
@@ -19553,22 +19553,22 @@
         </is>
       </c>
       <c r="I331">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J331">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K331">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L331">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M331">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N331">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="332">
@@ -19611,22 +19611,22 @@
         </is>
       </c>
       <c r="I332">
-        <v>0.6641186302686938</v>
+        <v>0.6642708613975647</v>
       </c>
       <c r="J332">
-        <v>0.002613431798127484</v>
+        <v>0.002357343008159838</v>
       </c>
       <c r="K332">
-        <v>9.381624198861306E-05</v>
+        <v>5.016247265672697E-05</v>
       </c>
       <c r="L332">
-        <v>0.6648418865360668</v>
+        <v>0.6649741119374146</v>
       </c>
       <c r="M332">
-        <v>0.6590994327209657</v>
+        <v>0.6596749939278006</v>
       </c>
       <c r="N332">
-        <v>0.6666663022977295</v>
+        <v>0.6666663138756296</v>
       </c>
     </row>
     <row r="333">
@@ -19669,22 +19669,22 @@
         </is>
       </c>
       <c r="I333">
-        <v>0.3358813697313062</v>
+        <v>0.3357291386024353</v>
       </c>
       <c r="J333">
-        <v>0.002613431798127484</v>
+        <v>0.002357343008159839</v>
       </c>
       <c r="K333">
-        <v>9.381624198861271E-05</v>
+        <v>5.016247265672708E-05</v>
       </c>
       <c r="L333">
-        <v>0.3351581134639331</v>
+        <v>0.3350258880625854</v>
       </c>
       <c r="M333">
-        <v>0.3333336977022705</v>
+        <v>0.3333336861243703</v>
       </c>
       <c r="N333">
-        <v>0.3409005672790343</v>
+        <v>0.3403250060721993</v>
       </c>
     </row>
     <row r="334">
@@ -19727,22 +19727,22 @@
         </is>
       </c>
       <c r="I334">
-        <v>1.011557198215439</v>
+        <v>1.010858184148251</v>
       </c>
       <c r="J334">
-        <v>0.0119555746509837</v>
+        <v>0.01075827224867086</v>
       </c>
       <c r="K334">
-        <v>0.0004308166369061459</v>
+        <v>0.0002292629789821314</v>
       </c>
       <c r="L334">
-        <v>1.008234048580363</v>
+        <v>1.007635882505233</v>
       </c>
       <c r="M334">
-        <v>1.000001639661113</v>
+        <v>1.000001587560507</v>
       </c>
       <c r="N334">
-        <v>1.034443515970547</v>
+        <v>1.031795988039064</v>
       </c>
     </row>
     <row r="335">
@@ -19785,22 +19785,22 @@
         </is>
       </c>
       <c r="I335">
-        <v>0.010370140030249</v>
+        <v>0.01051965244799468</v>
       </c>
       <c r="J335">
-        <v>0.01008191102340146</v>
+        <v>0.01042131091402868</v>
       </c>
       <c r="K335">
-        <v>0.0003145735421965924</v>
+        <v>0.0002178348259680769</v>
       </c>
       <c r="L335">
-        <v>0.007451785075054682</v>
+        <v>0.00730961571359073</v>
       </c>
       <c r="M335">
-        <v>5.534907971185832E-07</v>
+        <v>3.035204062771645E-06</v>
       </c>
       <c r="N335">
-        <v>0.03008626983310624</v>
+        <v>0.0312612708638887</v>
       </c>
     </row>
     <row r="336">
@@ -19843,22 +19843,22 @@
         </is>
       </c>
       <c r="I336">
-        <v>0.1258487896051734</v>
+        <v>0.1258345179695498</v>
       </c>
       <c r="J336">
-        <v>0.0007490006050044072</v>
+        <v>0.0007413213044093456</v>
       </c>
       <c r="K336">
-        <v>2.250023393496862E-05</v>
+        <v>1.329965057658368E-05</v>
       </c>
       <c r="L336">
-        <v>0.1258909119043385</v>
+        <v>0.1258801095792167</v>
       </c>
       <c r="M336">
-        <v>0.1244034764949756</v>
+        <v>0.1243577255099199</v>
       </c>
       <c r="N336">
-        <v>0.1273052487090867</v>
+        <v>0.1272528992087051</v>
       </c>
     </row>
     <row r="337">
@@ -19901,22 +19901,22 @@
         </is>
       </c>
       <c r="I337">
-        <v>0.06371704026670297</v>
+        <v>0.06366761678554783</v>
       </c>
       <c r="J337">
-        <v>0.0005841059308387508</v>
+        <v>0.0005342838785689983</v>
       </c>
       <c r="K337">
-        <v>2.034605179351577E-05</v>
+        <v>1.038571457808296E-05</v>
       </c>
       <c r="L337">
-        <v>0.06362399146240541</v>
+        <v>0.06359989551439847</v>
       </c>
       <c r="M337">
-        <v>0.06278188874215113</v>
+        <v>0.06274015613768184</v>
       </c>
       <c r="N337">
-        <v>0.06491019915404349</v>
+        <v>0.06476679422928319</v>
       </c>
     </row>
     <row r="338">
@@ -19959,22 +19959,22 @@
         </is>
       </c>
       <c r="I338">
-        <v>0.09125447553270249</v>
+        <v>0.09106027021934722</v>
       </c>
       <c r="J338">
-        <v>0.002913049482030947</v>
+        <v>0.002966505740861798</v>
       </c>
       <c r="K338">
-        <v>7.881754910702992E-05</v>
+        <v>5.211217384165402E-05</v>
       </c>
       <c r="L338">
-        <v>0.09122397355060981</v>
+        <v>0.0910640919040135</v>
       </c>
       <c r="M338">
-        <v>0.08579485592096404</v>
+        <v>0.0853939231227054</v>
       </c>
       <c r="N338">
-        <v>0.09719132461815057</v>
+        <v>0.09700744137242577</v>
       </c>
     </row>
     <row r="339">
@@ -20017,22 +20017,22 @@
         </is>
       </c>
       <c r="I339">
-        <v>0.04649770199450558</v>
+        <v>0.04637346409278303</v>
       </c>
       <c r="J339">
-        <v>0.001545892051463441</v>
+        <v>0.001542824598922063</v>
       </c>
       <c r="K339">
-        <v>4.424430803368853E-05</v>
+        <v>2.687047152778124E-05</v>
       </c>
       <c r="L339">
-        <v>0.04648513188188992</v>
+        <v>0.04637223933659133</v>
       </c>
       <c r="M339">
-        <v>0.04355768716772455</v>
+        <v>0.04342456076350146</v>
       </c>
       <c r="N339">
-        <v>0.04954835624834615</v>
+        <v>0.04940495340937583</v>
       </c>
     </row>
     <row r="340">
@@ -20075,22 +20075,22 @@
         </is>
       </c>
       <c r="I340">
-        <v>0.04808237925543987</v>
+        <v>0.04779046743573452</v>
       </c>
       <c r="J340">
-        <v>0.004142226875569896</v>
+        <v>0.004193489889832808</v>
       </c>
       <c r="K340">
-        <v>0.0001124008759338577</v>
+        <v>7.34804036482338E-05</v>
       </c>
       <c r="L340">
-        <v>0.04796774927696158</v>
+        <v>0.04768958444714324</v>
       </c>
       <c r="M340">
-        <v>0.04037530649907889</v>
+        <v>0.03957283535360455</v>
       </c>
       <c r="N340">
-        <v>0.05673238218088082</v>
+        <v>0.05590466577499529</v>
       </c>
     </row>
     <row r="341">
@@ -20133,22 +20133,22 @@
         </is>
       </c>
       <c r="I341">
-        <v>0.02481570922370386</v>
+        <v>0.02465735063902469</v>
       </c>
       <c r="J341">
-        <v>0.002174174555693733</v>
+        <v>0.002185132242798985</v>
       </c>
       <c r="K341">
-        <v>6.094887956386524E-05</v>
+        <v>3.775599709925427E-05</v>
       </c>
       <c r="L341">
-        <v>0.02473670745279042</v>
+        <v>0.02458428570939757</v>
       </c>
       <c r="M341">
-        <v>0.02075224204205434</v>
+        <v>0.02051661778773792</v>
       </c>
       <c r="N341">
-        <v>0.02920743563372965</v>
+        <v>0.02904358464714579</v>
       </c>
     </row>
     <row r="342">
@@ -20191,22 +20191,22 @@
         </is>
       </c>
       <c r="I342">
-        <v>0.01848769677962476</v>
+        <v>0.01826999464690852</v>
       </c>
       <c r="J342">
-        <v>0.003106155478899864</v>
+        <v>0.003123396598778489</v>
       </c>
       <c r="K342">
-        <v>8.455532256517311E-05</v>
+        <v>5.456322063992267E-05</v>
       </c>
       <c r="L342">
-        <v>0.01827336822367226</v>
+        <v>0.01805670116753954</v>
       </c>
       <c r="M342">
-        <v>0.01291387824963854</v>
+        <v>0.01253747862523029</v>
       </c>
       <c r="N342">
-        <v>0.02516110058859209</v>
+        <v>0.02457302989622004</v>
       </c>
     </row>
     <row r="343">
@@ -20249,22 +20249,22 @@
         </is>
       </c>
       <c r="I343">
-        <v>0.009728033043400539</v>
+        <v>0.009613789963538483</v>
       </c>
       <c r="J343">
-        <v>0.001656559538795364</v>
+        <v>0.001659710961352733</v>
       </c>
       <c r="K343">
-        <v>4.6335152869916E-05</v>
+        <v>2.860342543478354E-05</v>
       </c>
       <c r="L343">
-        <v>0.009607564608013517</v>
+        <v>0.009493398199156081</v>
       </c>
       <c r="M343">
-        <v>0.006862171094813861</v>
+        <v>0.006577597005322361</v>
       </c>
       <c r="N343">
-        <v>0.01330483055239388</v>
+        <v>0.01299403612039333</v>
       </c>
     </row>
     <row r="344">
@@ -20307,22 +20307,22 @@
         </is>
       </c>
       <c r="I344">
-        <v>0.005220234655217587</v>
+        <v>0.005121013944093588</v>
       </c>
       <c r="J344">
-        <v>0.001456598426889403</v>
+        <v>0.001453488374563846</v>
       </c>
       <c r="K344">
-        <v>3.974811471445277E-05</v>
+        <v>2.52379793702746E-05</v>
       </c>
       <c r="L344">
-        <v>0.005041649373712145</v>
+        <v>0.004947582994171094</v>
       </c>
       <c r="M344">
-        <v>0.002630981919967121</v>
+        <v>0.002572285508220139</v>
       </c>
       <c r="N344">
-        <v>0.008269902417117685</v>
+        <v>0.008048554509674776</v>
       </c>
     </row>
     <row r="345">
@@ -20365,22 +20365,22 @@
         </is>
       </c>
       <c r="I345">
-        <v>0.002819306852193219</v>
+        <v>0.002767069161681853</v>
       </c>
       <c r="J345">
-        <v>0.0007967959562887942</v>
+        <v>0.000793902227942943</v>
       </c>
       <c r="K345">
-        <v>2.228990093275738E-05</v>
+        <v>1.362382666850888E-05</v>
       </c>
       <c r="L345">
-        <v>0.00272233955576463</v>
+        <v>0.002667922613598113</v>
       </c>
       <c r="M345">
-        <v>0.001456810073665405</v>
+        <v>0.001393009797483222</v>
       </c>
       <c r="N345">
-        <v>0.00449656317323801</v>
+        <v>0.00440658776345427</v>
       </c>
     </row>
     <row r="346">
@@ -20423,22 +20423,22 @@
         </is>
       </c>
       <c r="I346">
-        <v>34.86268718595983</v>
+        <v>34.75180857494147</v>
       </c>
       <c r="J346">
-        <v>1.530407767195968</v>
+        <v>1.542203422448353</v>
       </c>
       <c r="K346">
-        <v>0.04171509487278559</v>
+        <v>0.02699057652379192</v>
       </c>
       <c r="L346">
-        <v>34.78650917988247</v>
+        <v>34.68583666260966</v>
       </c>
       <c r="M346">
-        <v>32.22286680015628</v>
+        <v>31.71799219953405</v>
       </c>
       <c r="N346">
-        <v>38.26703389781364</v>
+        <v>37.72032318238269</v>
       </c>
     </row>
     <row r="347">
@@ -20481,22 +20481,22 @@
         </is>
       </c>
       <c r="I347">
-        <v>35.2281855078489</v>
+        <v>35.12140768963494</v>
       </c>
       <c r="J347">
-        <v>1.594168463608602</v>
+        <v>1.606142811826278</v>
       </c>
       <c r="K347">
-        <v>0.04436465933315753</v>
+        <v>0.02770732504743905</v>
       </c>
       <c r="L347">
-        <v>35.14874543285814</v>
+        <v>35.04006574650231</v>
       </c>
       <c r="M347">
-        <v>32.30503286216645</v>
+        <v>32.09570175455197</v>
       </c>
       <c r="N347">
-        <v>38.53019644175851</v>
+        <v>38.35798639973707</v>
       </c>
     </row>
     <row r="348">
@@ -20539,22 +20539,22 @@
         </is>
       </c>
       <c r="I348">
-        <v>3.550458937681949</v>
+        <v>3.547252186736515</v>
       </c>
       <c r="J348">
-        <v>0.04372901139278984</v>
+        <v>0.04421217739188651</v>
       </c>
       <c r="K348">
-        <v>0.001190263284833432</v>
+        <v>0.0007748579015542237</v>
       </c>
       <c r="L348">
-        <v>3.5492296443733</v>
+        <v>3.546331438288005</v>
       </c>
       <c r="M348">
-        <v>3.472676349587001</v>
+        <v>3.461894327328535</v>
       </c>
       <c r="N348">
-        <v>3.64458879180407</v>
+        <v>3.634803095994706</v>
       </c>
     </row>
     <row r="349">
@@ -46909,22 +46909,22 @@
         </is>
       </c>
       <c r="I2">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J2">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K2">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L2">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M2">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N2">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="3">
@@ -46967,22 +46967,22 @@
         </is>
       </c>
       <c r="I3">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J3">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K3">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L3">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M3">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N3">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="4">
@@ -47025,22 +47025,22 @@
         </is>
       </c>
       <c r="I4">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J4">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K4">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L4">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M4">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N4">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="5">
@@ -47083,22 +47083,22 @@
         </is>
       </c>
       <c r="I5">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J5">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K5">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L5">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M5">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N5">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="6">
@@ -47141,22 +47141,22 @@
         </is>
       </c>
       <c r="I6">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J6">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K6">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L6">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M6">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N6">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="7">
@@ -47199,22 +47199,22 @@
         </is>
       </c>
       <c r="I7">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J7">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K7">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L7">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M7">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N7">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="8">
@@ -47257,22 +47257,22 @@
         </is>
       </c>
       <c r="I8">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J8">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K8">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L8">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M8">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N8">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="9">
@@ -47315,22 +47315,22 @@
         </is>
       </c>
       <c r="I9">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J9">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K9">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L9">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M9">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N9">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="10">
@@ -47373,22 +47373,22 @@
         </is>
       </c>
       <c r="I10">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J10">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K10">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L10">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M10">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N10">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="11">
@@ -47431,22 +47431,22 @@
         </is>
       </c>
       <c r="I11">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J11">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K11">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L11">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M11">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N11">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="12">
@@ -47489,22 +47489,22 @@
         </is>
       </c>
       <c r="I12">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J12">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K12">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L12">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M12">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N12">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="13">
@@ -47547,22 +47547,22 @@
         </is>
       </c>
       <c r="I13">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J13">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K13">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L13">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M13">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N13">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="14">
@@ -47605,22 +47605,22 @@
         </is>
       </c>
       <c r="I14">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J14">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K14">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L14">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M14">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N14">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="15">
@@ -47663,22 +47663,22 @@
         </is>
       </c>
       <c r="I15">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J15">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K15">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L15">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M15">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N15">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="16">
@@ -47721,22 +47721,22 @@
         </is>
       </c>
       <c r="I16">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J16">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K16">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L16">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M16">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N16">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="17">
@@ -47779,22 +47779,22 @@
         </is>
       </c>
       <c r="I17">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J17">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K17">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L17">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M17">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N17">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="18">
@@ -47837,22 +47837,22 @@
         </is>
       </c>
       <c r="I18">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J18">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K18">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L18">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M18">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N18">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="19">
@@ -47895,22 +47895,22 @@
         </is>
       </c>
       <c r="I19">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J19">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K19">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L19">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M19">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N19">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="20">
@@ -47953,22 +47953,22 @@
         </is>
       </c>
       <c r="I20">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J20">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K20">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L20">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M20">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N20">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="21">
@@ -48011,22 +48011,22 @@
         </is>
       </c>
       <c r="I21">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J21">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K21">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L21">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M21">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N21">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="22">
@@ -48069,22 +48069,22 @@
         </is>
       </c>
       <c r="I22">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J22">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K22">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L22">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M22">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N22">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="23">
@@ -48127,22 +48127,22 @@
         </is>
       </c>
       <c r="I23">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J23">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K23">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L23">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M23">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N23">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="24">
@@ -48185,22 +48185,22 @@
         </is>
       </c>
       <c r="I24">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J24">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K24">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L24">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M24">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N24">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="25">
@@ -48243,22 +48243,22 @@
         </is>
       </c>
       <c r="I25">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J25">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K25">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L25">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M25">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N25">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="26">
@@ -48301,22 +48301,22 @@
         </is>
       </c>
       <c r="I26">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J26">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K26">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L26">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M26">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N26">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="27">
@@ -48359,22 +48359,22 @@
         </is>
       </c>
       <c r="I27">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J27">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K27">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L27">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M27">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N27">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="28">
@@ -48417,22 +48417,22 @@
         </is>
       </c>
       <c r="I28">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J28">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K28">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L28">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M28">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N28">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="29">
@@ -48475,22 +48475,22 @@
         </is>
       </c>
       <c r="I29">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J29">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K29">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L29">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M29">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N29">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="30">
@@ -48533,22 +48533,22 @@
         </is>
       </c>
       <c r="I30">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J30">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K30">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L30">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M30">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N30">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="31">
@@ -48591,22 +48591,22 @@
         </is>
       </c>
       <c r="I31">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J31">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K31">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L31">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M31">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N31">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="32">
@@ -48649,22 +48649,22 @@
         </is>
       </c>
       <c r="I32">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J32">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K32">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L32">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M32">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N32">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="33">
@@ -48707,22 +48707,22 @@
         </is>
       </c>
       <c r="I33">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J33">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K33">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L33">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M33">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N33">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="34">
@@ -48765,22 +48765,22 @@
         </is>
       </c>
       <c r="I34">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J34">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K34">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L34">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M34">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N34">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="35">
@@ -48823,22 +48823,22 @@
         </is>
       </c>
       <c r="I35">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J35">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K35">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L35">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M35">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N35">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="36">
@@ -48881,22 +48881,22 @@
         </is>
       </c>
       <c r="I36">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J36">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K36">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L36">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M36">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N36">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="37">
@@ -48939,22 +48939,22 @@
         </is>
       </c>
       <c r="I37">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J37">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K37">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L37">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M37">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N37">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="38">
@@ -48997,22 +48997,22 @@
         </is>
       </c>
       <c r="I38">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J38">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K38">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L38">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M38">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N38">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="39">
@@ -49055,22 +49055,22 @@
         </is>
       </c>
       <c r="I39">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J39">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K39">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L39">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M39">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N39">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="40">
@@ -49113,22 +49113,22 @@
         </is>
       </c>
       <c r="I40">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J40">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K40">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L40">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M40">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N40">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="41">
@@ -49171,22 +49171,22 @@
         </is>
       </c>
       <c r="I41">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J41">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K41">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L41">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M41">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N41">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="42">
@@ -49229,22 +49229,22 @@
         </is>
       </c>
       <c r="I42">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J42">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K42">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L42">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M42">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N42">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="43">
@@ -49287,22 +49287,22 @@
         </is>
       </c>
       <c r="I43">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J43">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K43">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L43">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M43">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N43">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="44">
@@ -49345,22 +49345,22 @@
         </is>
       </c>
       <c r="I44">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J44">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K44">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L44">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M44">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N44">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="45">
@@ -49403,22 +49403,22 @@
         </is>
       </c>
       <c r="I45">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J45">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K45">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L45">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M45">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N45">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="46">
@@ -49461,22 +49461,22 @@
         </is>
       </c>
       <c r="I46">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J46">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K46">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L46">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M46">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N46">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="47">
@@ -49519,22 +49519,22 @@
         </is>
       </c>
       <c r="I47">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J47">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K47">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L47">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M47">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N47">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="48">
@@ -49577,22 +49577,22 @@
         </is>
       </c>
       <c r="I48">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J48">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K48">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L48">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M48">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N48">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="49">
@@ -49635,22 +49635,22 @@
         </is>
       </c>
       <c r="I49">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J49">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K49">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L49">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M49">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N49">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="50">
@@ -49693,22 +49693,22 @@
         </is>
       </c>
       <c r="I50">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J50">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K50">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L50">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M50">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N50">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="51">
@@ -49751,22 +49751,22 @@
         </is>
       </c>
       <c r="I51">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J51">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K51">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L51">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M51">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N51">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="52">
@@ -49809,22 +49809,22 @@
         </is>
       </c>
       <c r="I52">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J52">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K52">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L52">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M52">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N52">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="53">
@@ -49867,22 +49867,22 @@
         </is>
       </c>
       <c r="I53">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J53">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K53">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L53">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M53">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N53">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="54">
@@ -49925,22 +49925,22 @@
         </is>
       </c>
       <c r="I54">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J54">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K54">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L54">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M54">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N54">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="55">
@@ -49983,22 +49983,22 @@
         </is>
       </c>
       <c r="I55">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J55">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K55">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L55">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M55">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N55">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="56">
@@ -50041,22 +50041,22 @@
         </is>
       </c>
       <c r="I56">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J56">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K56">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L56">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M56">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N56">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="57">
@@ -50099,22 +50099,22 @@
         </is>
       </c>
       <c r="I57">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J57">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K57">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L57">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M57">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N57">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="58">
@@ -50157,22 +50157,22 @@
         </is>
       </c>
       <c r="I58">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J58">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K58">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L58">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M58">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N58">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="59">
@@ -50215,22 +50215,22 @@
         </is>
       </c>
       <c r="I59">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J59">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K59">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L59">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M59">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N59">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="60">
@@ -50273,22 +50273,22 @@
         </is>
       </c>
       <c r="I60">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J60">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K60">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L60">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M60">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N60">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="61">
@@ -50331,22 +50331,22 @@
         </is>
       </c>
       <c r="I61">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J61">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K61">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L61">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M61">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N61">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="62">
@@ -50389,22 +50389,22 @@
         </is>
       </c>
       <c r="I62">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J62">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K62">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L62">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M62">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N62">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="63">
@@ -50447,22 +50447,22 @@
         </is>
       </c>
       <c r="I63">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J63">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K63">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L63">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M63">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N63">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="64">
@@ -50505,22 +50505,22 @@
         </is>
       </c>
       <c r="I64">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J64">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K64">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L64">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M64">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N64">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="65">
@@ -50563,22 +50563,22 @@
         </is>
       </c>
       <c r="I65">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J65">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K65">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L65">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M65">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N65">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="66">
@@ -50621,22 +50621,22 @@
         </is>
       </c>
       <c r="I66">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J66">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K66">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L66">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M66">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N66">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="67">
@@ -50679,22 +50679,22 @@
         </is>
       </c>
       <c r="I67">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J67">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K67">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L67">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M67">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N67">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="68">
@@ -50737,22 +50737,22 @@
         </is>
       </c>
       <c r="I68">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J68">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K68">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L68">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M68">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N68">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="69">
@@ -50795,22 +50795,22 @@
         </is>
       </c>
       <c r="I69">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J69">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K69">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L69">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M69">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N69">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="70">
@@ -50853,22 +50853,22 @@
         </is>
       </c>
       <c r="I70">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J70">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K70">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L70">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M70">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N70">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="71">
@@ -50911,22 +50911,22 @@
         </is>
       </c>
       <c r="I71">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J71">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K71">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L71">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M71">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N71">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="72">
@@ -50969,22 +50969,22 @@
         </is>
       </c>
       <c r="I72">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J72">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K72">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L72">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M72">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N72">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="73">
@@ -51027,22 +51027,22 @@
         </is>
       </c>
       <c r="I73">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J73">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K73">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L73">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M73">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N73">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="74">
@@ -51085,22 +51085,22 @@
         </is>
       </c>
       <c r="I74">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J74">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K74">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L74">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M74">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N74">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="75">
@@ -51143,22 +51143,22 @@
         </is>
       </c>
       <c r="I75">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J75">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K75">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L75">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M75">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N75">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="76">
@@ -51201,22 +51201,22 @@
         </is>
       </c>
       <c r="I76">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J76">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K76">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L76">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M76">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N76">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="77">
@@ -51259,22 +51259,22 @@
         </is>
       </c>
       <c r="I77">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J77">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K77">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L77">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M77">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N77">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="78">
@@ -51317,22 +51317,22 @@
         </is>
       </c>
       <c r="I78">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J78">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K78">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L78">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M78">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N78">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="79">
@@ -51375,22 +51375,22 @@
         </is>
       </c>
       <c r="I79">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J79">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K79">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L79">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M79">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N79">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="80">
@@ -51433,22 +51433,22 @@
         </is>
       </c>
       <c r="I80">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J80">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K80">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L80">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M80">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N80">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="81">
@@ -51491,22 +51491,22 @@
         </is>
       </c>
       <c r="I81">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J81">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K81">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L81">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M81">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N81">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="82">
@@ -51549,22 +51549,22 @@
         </is>
       </c>
       <c r="I82">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J82">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K82">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L82">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M82">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N82">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="83">
@@ -51607,22 +51607,22 @@
         </is>
       </c>
       <c r="I83">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J83">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K83">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L83">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M83">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N83">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="84">
@@ -51665,22 +51665,22 @@
         </is>
       </c>
       <c r="I84">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J84">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K84">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L84">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M84">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N84">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="85">
@@ -51723,22 +51723,22 @@
         </is>
       </c>
       <c r="I85">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J85">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K85">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L85">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M85">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N85">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="86">
@@ -51781,22 +51781,22 @@
         </is>
       </c>
       <c r="I86">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J86">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K86">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L86">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M86">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N86">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="87">
@@ -51839,22 +51839,22 @@
         </is>
       </c>
       <c r="I87">
-        <v>0.6642256356081376</v>
+        <v>0.6641976449030755</v>
       </c>
       <c r="J87">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K87">
-        <v>7.4879560723826E-05</v>
+        <v>4.822699826702867E-05</v>
       </c>
       <c r="L87">
-        <v>0.6649444447198314</v>
+        <v>0.6649107887486667</v>
       </c>
       <c r="M87">
-        <v>0.6594640717734882</v>
+        <v>0.659291297760771</v>
       </c>
       <c r="N87">
-        <v>0.6666650177245034</v>
+        <v>0.6666666039965141</v>
       </c>
     </row>
     <row r="88">
@@ -51897,22 +51897,22 @@
         </is>
       </c>
       <c r="I88">
-        <v>0.3357743643918624</v>
+        <v>0.3358023550969244</v>
       </c>
       <c r="J88">
-        <v>0.002376328042686348</v>
+        <v>0.002395218689882778</v>
       </c>
       <c r="K88">
-        <v>7.487956072382592E-05</v>
+        <v>4.822699826702903E-05</v>
       </c>
       <c r="L88">
-        <v>0.3350555552801687</v>
+        <v>0.3350892112513333</v>
       </c>
       <c r="M88">
-        <v>0.3333349822754967</v>
+        <v>0.3333333960034859</v>
       </c>
       <c r="N88">
-        <v>0.3405359282265117</v>
+        <v>0.3407087022392289</v>
       </c>
     </row>
     <row r="89">
@@ -51955,22 +51955,22 @@
         </is>
       </c>
       <c r="I89">
-        <v>1.011063799313621</v>
+        <v>1.011191310800068</v>
       </c>
       <c r="J89">
-        <v>0.01084388231914484</v>
+        <v>0.01092942846376453</v>
       </c>
       <c r="K89">
-        <v>0.0003417593662332105</v>
+        <v>0.0002203199161699112</v>
       </c>
       <c r="L89">
-        <v>1.007770071442108</v>
+        <v>1.007922316562066</v>
       </c>
       <c r="M89">
-        <v>1.000007420258089</v>
+        <v>1.000000282015713</v>
       </c>
       <c r="N89">
-        <v>1.032765673831822</v>
+        <v>1.033560441026351</v>
       </c>
     </row>
     <row r="90">
@@ -52013,22 +52013,22 @@
         </is>
       </c>
       <c r="I90">
-        <v>0.01033349396797079</v>
+        <v>0.01071271976451468</v>
       </c>
       <c r="J90">
-        <v>0.01013854161016919</v>
+        <v>0.01072521988750751</v>
       </c>
       <c r="K90">
-        <v>0.0003394641961931578</v>
+        <v>0.0002242905975208711</v>
       </c>
       <c r="L90">
-        <v>0.007124058883376402</v>
+        <v>0.007315251019662291</v>
       </c>
       <c r="M90">
-        <v>4.227659213634511E-06</v>
+        <v>2.065368471734774E-09</v>
       </c>
       <c r="N90">
-        <v>0.03122120561225397</v>
+        <v>0.03221700234560272</v>
       </c>
     </row>
     <row r="91">
@@ -52071,22 +52071,22 @@
         </is>
       </c>
       <c r="I91">
-        <v>0.1258186861868515</v>
+        <v>0.1258387323037746</v>
       </c>
       <c r="J91">
-        <v>0.0007321394454587419</v>
+        <v>0.0007500427512261036</v>
       </c>
       <c r="K91">
-        <v>2.054438546839922E-05</v>
+        <v>1.325661844284839E-05</v>
       </c>
       <c r="L91">
-        <v>0.1258647337934256</v>
+        <v>0.1258872430716971</v>
       </c>
       <c r="M91">
-        <v>0.1242858847607401</v>
+        <v>0.1242809053181195</v>
       </c>
       <c r="N91">
-        <v>0.1271227905860693</v>
+        <v>0.1272169964382449</v>
       </c>
     </row>
     <row r="92">
@@ -52129,22 +52129,22 @@
         </is>
       </c>
       <c r="I92">
-        <v>0.06367138671860575</v>
+        <v>0.06369175709494113</v>
       </c>
       <c r="J92">
-        <v>0.0005432786998588684</v>
+        <v>0.0005451360253805939</v>
       </c>
       <c r="K92">
-        <v>1.659870532930396E-05</v>
+        <v>1.033314028091954E-05</v>
       </c>
       <c r="L92">
-        <v>0.06358946388967585</v>
+        <v>0.06361442609030421</v>
       </c>
       <c r="M92">
-        <v>0.06274558492991726</v>
+        <v>0.06272239555962413</v>
       </c>
       <c r="N92">
-        <v>0.06482878680796773</v>
+        <v>0.06479943357706675</v>
       </c>
     </row>
     <row r="93">
@@ -52187,22 +52187,22 @@
         </is>
       </c>
       <c r="I93">
-        <v>0.0910164629363638</v>
+        <v>0.09114209269142348</v>
       </c>
       <c r="J93">
-        <v>0.002921443261309493</v>
+        <v>0.003006199531722789</v>
       </c>
       <c r="K93">
-        <v>7.529776236112953E-05</v>
+        <v>4.947982810098368E-05</v>
       </c>
       <c r="L93">
-        <v>0.09097070567763062</v>
+        <v>0.09113554619823204</v>
       </c>
       <c r="M93">
-        <v>0.08517992431748296</v>
+        <v>0.08505929742430067</v>
       </c>
       <c r="N93">
-        <v>0.09661628634901658</v>
+        <v>0.09679447989134632</v>
       </c>
     </row>
     <row r="94">
@@ -52245,22 +52245,22 @@
         </is>
       </c>
       <c r="I94">
-        <v>0.04635498986375427</v>
+        <v>0.04643594794268728</v>
       </c>
       <c r="J94">
-        <v>0.001538116205268203</v>
+        <v>0.00156762695835429</v>
       </c>
       <c r="K94">
-        <v>4.146641645660172E-05</v>
+        <v>2.629522787526456E-05</v>
       </c>
       <c r="L94">
-        <v>0.04632186224483549</v>
+        <v>0.04642911429129068</v>
       </c>
       <c r="M94">
-        <v>0.04349219131146365</v>
+        <v>0.04330088569529806</v>
       </c>
       <c r="N94">
-        <v>0.04954389239270522</v>
+        <v>0.04944517396148373</v>
       </c>
     </row>
     <row r="95">
@@ -52303,22 +52303,22 @@
         </is>
       </c>
       <c r="I95">
-        <v>0.04773062142444651</v>
+        <v>0.04791910712605641</v>
       </c>
       <c r="J95">
-        <v>0.004133848315774955</v>
+        <v>0.004259190652269667</v>
       </c>
       <c r="K95">
-        <v>0.0001063285105799933</v>
+        <v>6.991441116231795E-05</v>
       </c>
       <c r="L95">
-        <v>0.04755829117983798</v>
+        <v>0.04777953014866183</v>
       </c>
       <c r="M95">
-        <v>0.03974507185895487</v>
+        <v>0.03935440234386017</v>
       </c>
       <c r="N95">
-        <v>0.05580834636870117</v>
+        <v>0.05597231942521083</v>
       </c>
     </row>
     <row r="96">
@@ -52361,22 +52361,22 @@
         </is>
       </c>
       <c r="I96">
-        <v>0.02462382428971555</v>
+        <v>0.02473985381919177</v>
       </c>
       <c r="J96">
-        <v>0.002167660416785718</v>
+        <v>0.002221227488413244</v>
       </c>
       <c r="K96">
-        <v>5.774709475441528E-05</v>
+        <v>3.727418524761849E-05</v>
       </c>
       <c r="L96">
-        <v>0.02453495331414481</v>
+        <v>0.02467012218091848</v>
       </c>
       <c r="M96">
-        <v>0.0203742449338244</v>
+        <v>0.02054972564633692</v>
       </c>
       <c r="N96">
-        <v>0.02889017033763636</v>
+        <v>0.02925643591890296</v>
       </c>
     </row>
     <row r="97">
@@ -52419,22 +52419,22 @@
         </is>
       </c>
       <c r="I97">
-        <v>0.01822345586115398</v>
+        <v>0.01837122568580211</v>
       </c>
       <c r="J97">
-        <v>0.003079570963703863</v>
+        <v>0.003182882430492792</v>
       </c>
       <c r="K97">
-        <v>7.997196901908247E-05</v>
+        <v>5.211466742479226E-05</v>
       </c>
       <c r="L97">
-        <v>0.01797653156094862</v>
+        <v>0.01813787889449251</v>
       </c>
       <c r="M97">
-        <v>0.01263837478351525</v>
+        <v>0.01235366873627036</v>
       </c>
       <c r="N97">
-        <v>0.02447565553033111</v>
+        <v>0.02458231769339083</v>
       </c>
     </row>
     <row r="98">
@@ -52477,22 +52477,22 @@
         </is>
       </c>
       <c r="I98">
-        <v>0.009585824537373644</v>
+        <v>0.009676264711520732</v>
       </c>
       <c r="J98">
-        <v>0.001642924194303671</v>
+        <v>0.001692177421222864</v>
       </c>
       <c r="K98">
-        <v>4.355674142323058E-05</v>
+        <v>2.835905731172752E-05</v>
       </c>
       <c r="L98">
-        <v>0.009462259577995569</v>
+        <v>0.009552672792308505</v>
       </c>
       <c r="M98">
-        <v>0.006663357583391445</v>
+        <v>0.006437672580998526</v>
       </c>
       <c r="N98">
-        <v>0.01308470234237474</v>
+        <v>0.01300251920285405</v>
       </c>
     </row>
     <row r="99">
@@ -52535,22 +52535,22 @@
         </is>
       </c>
       <c r="I99">
-        <v>0.005097967219381412</v>
+        <v>0.005170395234794015</v>
       </c>
       <c r="J99">
-        <v>0.001431958750845945</v>
+        <v>0.001488498988196772</v>
       </c>
       <c r="K99">
-        <v>3.69256669574069E-05</v>
+        <v>2.424790499066719E-05</v>
       </c>
       <c r="L99">
-        <v>0.004913093890338767</v>
+        <v>0.004982435581495512</v>
       </c>
       <c r="M99">
-        <v>0.002535670537177131</v>
+        <v>0.002583541239242071</v>
       </c>
       <c r="N99">
-        <v>0.00790760942910965</v>
+        <v>0.008137263344745278</v>
       </c>
     </row>
     <row r="100">
@@ -52593,22 +52593,22 @@
         </is>
       </c>
       <c r="I100">
-        <v>0.002752801248824459</v>
+        <v>0.002797489789700046</v>
       </c>
       <c r="J100">
-        <v>0.0007840636536847119</v>
+        <v>0.0008139206057876888</v>
       </c>
       <c r="K100">
-        <v>1.987870838352438E-05</v>
+        <v>1.362228454906681E-05</v>
       </c>
       <c r="L100">
-        <v>0.002652558292393608</v>
+        <v>0.002694486491152702</v>
       </c>
       <c r="M100">
-        <v>0.001386239718644866</v>
+        <v>0.001346685410384022</v>
       </c>
       <c r="N100">
-        <v>0.004370987631858155</v>
+        <v>0.004410996770091128</v>
       </c>
     </row>
     <row r="101">
@@ -52651,22 +52651,22 @@
         </is>
       </c>
       <c r="I101">
-        <v>34.73035918773104</v>
+        <v>34.80202436799755</v>
       </c>
       <c r="J101">
-        <v>1.520970800550962</v>
+        <v>1.569482358671988</v>
       </c>
       <c r="K101">
-        <v>0.03957632790620449</v>
+        <v>0.02573436677965579</v>
       </c>
       <c r="L101">
-        <v>34.64704149057644</v>
+        <v>34.72046888830125</v>
       </c>
       <c r="M101">
-        <v>31.83842606548577</v>
+        <v>31.67636454895171</v>
       </c>
       <c r="N101">
-        <v>37.73388826787793</v>
+        <v>37.77079876653887</v>
       </c>
     </row>
     <row r="102">
@@ -52709,22 +52709,22 @@
         </is>
       </c>
       <c r="I102">
-        <v>35.09331665767908</v>
+        <v>35.17900290206794</v>
       </c>
       <c r="J102">
-        <v>1.587328181531894</v>
+        <v>1.63460070994861</v>
       </c>
       <c r="K102">
-        <v>0.04209201458086188</v>
+        <v>0.02740271545278867</v>
       </c>
       <c r="L102">
-        <v>35.00532525662735</v>
+        <v>35.09499213226917</v>
       </c>
       <c r="M102">
-        <v>32.17917408494985</v>
+        <v>31.95195799132502</v>
       </c>
       <c r="N102">
-        <v>38.41065647769564</v>
+        <v>38.32732105544031</v>
       </c>
     </row>
     <row r="103">
@@ -52767,22 +52767,22 @@
         </is>
       </c>
       <c r="I103">
-        <v>3.546661177776064</v>
+        <v>3.548664575829767</v>
       </c>
       <c r="J103">
-        <v>0.04360400263002171</v>
+        <v>0.04491392745958372</v>
       </c>
       <c r="K103">
-        <v>0.001136527325073034</v>
+        <v>0.000737231075732104</v>
       </c>
       <c r="L103">
-        <v>3.545212339277219</v>
+        <v>3.547329394546024</v>
       </c>
       <c r="M103">
-        <v>3.463906384642588</v>
+        <v>3.459347632098588</v>
       </c>
       <c r="N103">
-        <v>3.633668399878572</v>
+        <v>3.634772210384973</v>
       </c>
     </row>
     <row r="104">
@@ -52825,22 +52825,22 @@
         </is>
       </c>
       <c r="I104">
-        <v>0.6641186302686938</v>
+        <v>0.6642708613975647</v>
       </c>
       <c r="J104">
-        <v>0.002613431798127484</v>
+        <v>0.002357343008159838</v>
       </c>
       <c r="K104">
-        <v>9.381624198861306E-05</v>
+        <v>5.016247265672697E-05</v>
       </c>
       <c r="L104">
-        <v>0.6648418865360668</v>
+        <v>0.6649741119374146</v>
       </c>
       <c r="M104">
-        <v>0.6590994327209657</v>
+        <v>0.6596749939278006</v>
       </c>
       <c r="N104">
-        <v>0.6666663022977295</v>
+        <v>0.6666663138756296</v>
       </c>
     </row>
     <row r="105">
@@ -52883,22 +52883,22 @@
         </is>
       </c>
       <c r="I105">
-        <v>0.3358813697313062</v>
+        <v>0.3357291386024353</v>
       </c>
       <c r="J105">
-        <v>0.002613431798127484</v>
+        <v>0.002357343008159839</v>
       </c>
       <c r="K105">
-        <v>9.381624198861271E-05</v>
+        <v>5.016247265672708E-05</v>
       </c>
       <c r="L105">
-        <v>0.3351581134639331</v>
+        <v>0.3350258880625854</v>
       </c>
       <c r="M105">
-        <v>0.3333336977022705</v>
+        <v>0.3333336861243703</v>
       </c>
       <c r="N105">
-        <v>0.3409005672790343</v>
+        <v>0.3403250060721993</v>
       </c>
     </row>
     <row r="106">
@@ -52941,22 +52941,22 @@
         </is>
       </c>
       <c r="I106">
-        <v>1.011557198215439</v>
+        <v>1.010858184148251</v>
       </c>
       <c r="J106">
-        <v>0.0119555746509837</v>
+        <v>0.01075827224867086</v>
       </c>
       <c r="K106">
-        <v>0.0004308166369061459</v>
+        <v>0.0002292629789821314</v>
       </c>
       <c r="L106">
-        <v>1.008234048580363</v>
+        <v>1.007635882505233</v>
       </c>
       <c r="M106">
-        <v>1.000001639661113</v>
+        <v>1.000001587560507</v>
       </c>
       <c r="N106">
-        <v>1.034443515970547</v>
+        <v>1.031795988039064</v>
       </c>
     </row>
     <row r="107">
@@ -52999,22 +52999,22 @@
         </is>
       </c>
       <c r="I107">
-        <v>0.010370140030249</v>
+        <v>0.01051965244799468</v>
       </c>
       <c r="J107">
-        <v>0.01008191102340146</v>
+        <v>0.01042131091402868</v>
       </c>
       <c r="K107">
-        <v>0.0003145735421965924</v>
+        <v>0.0002178348259680769</v>
       </c>
       <c r="L107">
-        <v>0.007451785075054682</v>
+        <v>0.00730961571359073</v>
       </c>
       <c r="M107">
-        <v>5.534907971185832E-07</v>
+        <v>3.035204062771645E-06</v>
       </c>
       <c r="N107">
-        <v>0.03008626983310624</v>
+        <v>0.0312612708638887</v>
       </c>
     </row>
     <row r="108">
@@ -53057,22 +53057,22 @@
         </is>
       </c>
       <c r="I108">
-        <v>0.1258487896051734</v>
+        <v>0.1258345179695498</v>
       </c>
       <c r="J108">
-        <v>0.0007490006050044072</v>
+        <v>0.0007413213044093456</v>
       </c>
       <c r="K108">
-        <v>2.250023393496862E-05</v>
+        <v>1.329965057658368E-05</v>
       </c>
       <c r="L108">
-        <v>0.1258909119043385</v>
+        <v>0.1258801095792167</v>
       </c>
       <c r="M108">
-        <v>0.1244034764949756</v>
+        <v>0.1243577255099199</v>
       </c>
       <c r="N108">
-        <v>0.1273052487090867</v>
+        <v>0.1272528992087051</v>
       </c>
     </row>
     <row r="109">
@@ -53115,22 +53115,22 @@
         </is>
       </c>
       <c r="I109">
-        <v>0.06371704026670297</v>
+        <v>0.06366761678554783</v>
       </c>
       <c r="J109">
-        <v>0.0005841059308387508</v>
+        <v>0.0005342838785689983</v>
       </c>
       <c r="K109">
-        <v>2.034605179351577E-05</v>
+        <v>1.038571457808296E-05</v>
       </c>
       <c r="L109">
-        <v>0.06362399146240541</v>
+        <v>0.06359989551439847</v>
       </c>
       <c r="M109">
-        <v>0.06278188874215113</v>
+        <v>0.06274015613768184</v>
       </c>
       <c r="N109">
-        <v>0.06491019915404349</v>
+        <v>0.06476679422928319</v>
       </c>
     </row>
     <row r="110">
@@ -53173,22 +53173,22 @@
         </is>
       </c>
       <c r="I110">
-        <v>0.09125447553270249</v>
+        <v>0.09106027021934722</v>
       </c>
       <c r="J110">
-        <v>0.002913049482030947</v>
+        <v>0.002966505740861798</v>
       </c>
       <c r="K110">
-        <v>7.881754910702992E-05</v>
+        <v>5.211217384165402E-05</v>
       </c>
       <c r="L110">
-        <v>0.09122397355060981</v>
+        <v>0.0910640919040135</v>
       </c>
       <c r="M110">
-        <v>0.08579485592096404</v>
+        <v>0.0853939231227054</v>
       </c>
       <c r="N110">
-        <v>0.09719132461815057</v>
+        <v>0.09700744137242577</v>
       </c>
     </row>
     <row r="111">
@@ -53231,22 +53231,22 @@
         </is>
       </c>
       <c r="I111">
-        <v>0.04649770199450558</v>
+        <v>0.04637346409278303</v>
       </c>
       <c r="J111">
-        <v>0.001545892051463441</v>
+        <v>0.001542824598922063</v>
       </c>
       <c r="K111">
-        <v>4.424430803368853E-05</v>
+        <v>2.687047152778124E-05</v>
       </c>
       <c r="L111">
-        <v>0.04648513188188992</v>
+        <v>0.04637223933659133</v>
       </c>
       <c r="M111">
-        <v>0.04355768716772455</v>
+        <v>0.04342456076350146</v>
       </c>
       <c r="N111">
-        <v>0.04954835624834615</v>
+        <v>0.04940495340937583</v>
       </c>
     </row>
     <row r="112">
@@ -53289,22 +53289,22 @@
         </is>
       </c>
       <c r="I112">
-        <v>0.04808237925543987</v>
+        <v>0.04779046743573452</v>
       </c>
       <c r="J112">
-        <v>0.004142226875569896</v>
+        <v>0.004193489889832808</v>
       </c>
       <c r="K112">
-        <v>0.0001124008759338577</v>
+        <v>7.34804036482338E-05</v>
       </c>
       <c r="L112">
-        <v>0.04796774927696158</v>
+        <v>0.04768958444714324</v>
       </c>
       <c r="M112">
-        <v>0.04037530649907889</v>
+        <v>0.03957283535360455</v>
       </c>
       <c r="N112">
-        <v>0.05673238218088082</v>
+        <v>0.05590466577499529</v>
       </c>
     </row>
     <row r="113">
@@ -53347,22 +53347,22 @@
         </is>
       </c>
       <c r="I113">
-        <v>0.02481570922370386</v>
+        <v>0.02465735063902469</v>
       </c>
       <c r="J113">
-        <v>0.002174174555693733</v>
+        <v>0.002185132242798985</v>
       </c>
       <c r="K113">
-        <v>6.094887956386524E-05</v>
+        <v>3.775599709925427E-05</v>
       </c>
       <c r="L113">
-        <v>0.02473670745279042</v>
+        <v>0.02458428570939757</v>
       </c>
       <c r="M113">
-        <v>0.02075224204205434</v>
+        <v>0.02051661778773792</v>
       </c>
       <c r="N113">
-        <v>0.02920743563372965</v>
+        <v>0.02904358464714579</v>
       </c>
     </row>
     <row r="114">
@@ -53405,22 +53405,22 @@
         </is>
       </c>
       <c r="I114">
-        <v>0.01848769677962476</v>
+        <v>0.01826999464690852</v>
       </c>
       <c r="J114">
-        <v>0.003106155478899864</v>
+        <v>0.003123396598778489</v>
       </c>
       <c r="K114">
-        <v>8.455532256517311E-05</v>
+        <v>5.456322063992267E-05</v>
       </c>
       <c r="L114">
-        <v>0.01827336822367226</v>
+        <v>0.01805670116753954</v>
       </c>
       <c r="M114">
-        <v>0.01291387824963854</v>
+        <v>0.01253747862523029</v>
       </c>
       <c r="N114">
-        <v>0.02516110058859209</v>
+        <v>0.02457302989622004</v>
       </c>
     </row>
     <row r="115">
@@ -53463,22 +53463,22 @@
         </is>
       </c>
       <c r="I115">
-        <v>0.009728033043400539</v>
+        <v>0.009613789963538483</v>
       </c>
       <c r="J115">
-        <v>0.001656559538795364</v>
+        <v>0.001659710961352733</v>
       </c>
       <c r="K115">
-        <v>4.6335152869916E-05</v>
+        <v>2.860342543478354E-05</v>
       </c>
       <c r="L115">
-        <v>0.009607564608013517</v>
+        <v>0.009493398199156081</v>
       </c>
       <c r="M115">
-        <v>0.006862171094813861</v>
+        <v>0.006577597005322361</v>
       </c>
       <c r="N115">
-        <v>0.01330483055239388</v>
+        <v>0.01299403612039333</v>
       </c>
     </row>
     <row r="116">
@@ -53521,22 +53521,22 @@
         </is>
       </c>
       <c r="I116">
-        <v>0.005220234655217587</v>
+        <v>0.005121013944093588</v>
       </c>
       <c r="J116">
-        <v>0.001456598426889403</v>
+        <v>0.001453488374563846</v>
       </c>
       <c r="K116">
-        <v>3.974811471445277E-05</v>
+        <v>2.52379793702746E-05</v>
       </c>
       <c r="L116">
-        <v>0.005041649373712145</v>
+        <v>0.004947582994171094</v>
       </c>
       <c r="M116">
-        <v>0.002630981919967121</v>
+        <v>0.002572285508220139</v>
       </c>
       <c r="N116">
-        <v>0.008269902417117685</v>
+        <v>0.008048554509674776</v>
       </c>
     </row>
     <row r="117">
@@ -53579,22 +53579,22 @@
         </is>
       </c>
       <c r="I117">
-        <v>0.002819306852193219</v>
+        <v>0.002767069161681853</v>
       </c>
       <c r="J117">
-        <v>0.0007967959562887942</v>
+        <v>0.000793902227942943</v>
       </c>
       <c r="K117">
-        <v>2.228990093275738E-05</v>
+        <v>1.362382666850888E-05</v>
       </c>
       <c r="L117">
-        <v>0.00272233955576463</v>
+        <v>0.002667922613598113</v>
       </c>
       <c r="M117">
-        <v>0.001456810073665405</v>
+        <v>0.001393009797483222</v>
       </c>
       <c r="N117">
-        <v>0.00449656317323801</v>
+        <v>0.00440658776345427</v>
       </c>
     </row>
     <row r="118">
@@ -53637,22 +53637,22 @@
         </is>
       </c>
       <c r="I118">
-        <v>34.86268718595983</v>
+        <v>34.75180857494147</v>
       </c>
       <c r="J118">
-        <v>1.530407767195968</v>
+        <v>1.542203422448353</v>
       </c>
       <c r="K118">
-        <v>0.04171509487278559</v>
+        <v>0.02699057652379192</v>
       </c>
       <c r="L118">
-        <v>34.78650917988247</v>
+        <v>34.68583666260966</v>
       </c>
       <c r="M118">
-        <v>32.22286680015628</v>
+        <v>31.71799219953405</v>
       </c>
       <c r="N118">
-        <v>38.26703389781364</v>
+        <v>37.72032318238269</v>
       </c>
     </row>
     <row r="119">
@@ -53695,22 +53695,22 @@
         </is>
       </c>
       <c r="I119">
-        <v>35.2281855078489</v>
+        <v>35.12140768963494</v>
       </c>
       <c r="J119">
-        <v>1.594168463608602</v>
+        <v>1.606142811826278</v>
       </c>
       <c r="K119">
-        <v>0.04436465933315753</v>
+        <v>0.02770732504743905</v>
       </c>
       <c r="L119">
-        <v>35.14874543285814</v>
+        <v>35.04006574650231</v>
       </c>
       <c r="M119">
-        <v>32.30503286216645</v>
+        <v>32.09570175455197</v>
       </c>
       <c r="N119">
-        <v>38.53019644175851</v>
+        <v>38.35798639973707</v>
       </c>
     </row>
     <row r="120">
@@ -53753,22 +53753,22 @@
         </is>
       </c>
       <c r="I120">
-        <v>3.550458937681949</v>
+        <v>3.547252186736515</v>
       </c>
       <c r="J120">
-        <v>0.04372901139278984</v>
+        <v>0.04421217739188651</v>
       </c>
       <c r="K120">
-        <v>0.001190263284833432</v>
+        <v>0.0007748579015542237</v>
       </c>
       <c r="L120">
-        <v>3.5492296443733</v>
+        <v>3.546331438288005</v>
       </c>
       <c r="M120">
-        <v>3.472676349587001</v>
+        <v>3.461894327328535</v>
       </c>
       <c r="N120">
-        <v>3.64458879180407</v>
+        <v>3.634803095994706</v>
       </c>
     </row>
   </sheetData>
